--- a/reports/2026-09_月次実績報告/excel/第51期下期水産部部門別実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期下期水産部部門別実績.xlsx
@@ -20740,7 +20740,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>8</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F105" s="4" t="n"/>
       <c r="G105" s="4" t="n"/>
@@ -20756,7 +20756,7 @@
         <v/>
       </c>
       <c r="L105" s="4" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M105" s="4" t="n"/>
       <c r="N105" s="4" t="n"/>
@@ -21340,7 +21340,7 @@
         </is>
       </c>
       <c r="E113" s="20" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="F113" s="20" t="n">
         <v>205.68</v>
@@ -21362,7 +21362,7 @@
         <v/>
       </c>
       <c r="L113" s="20" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="M113" s="20" t="n">
         <v>26.08</v>
@@ -32129,10 +32129,10 @@
         </is>
       </c>
       <c r="E105" s="20" t="n">
-        <v>7432.895</v>
+        <v>7304.095</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>5654</v>
+        <v>5653.523</v>
       </c>
       <c r="G105" s="109" t="n">
         <v>2372.437</v>
@@ -32151,10 +32151,10 @@
         <v/>
       </c>
       <c r="L105" s="20" t="n">
-        <v>1476.758</v>
+        <v>1347.958</v>
       </c>
       <c r="M105" s="4" t="n">
-        <v>1043</v>
+        <v>1042.552</v>
       </c>
       <c r="N105" s="110" t="n">
         <v>426.527</v>
@@ -32213,7 +32213,7 @@
         </is>
       </c>
       <c r="E106" s="20" t="n">
-        <v>8579.040999999999</v>
+        <v>8504.615</v>
       </c>
       <c r="F106" s="20" t="n">
         <v>10766.038</v>
@@ -32235,7 +32235,7 @@
         <v/>
       </c>
       <c r="L106" s="20" t="n">
-        <v>3333.44</v>
+        <v>3249.343</v>
       </c>
       <c r="M106" s="4" t="n">
         <v>4060.094</v>
@@ -32381,7 +32381,7 @@
         </is>
       </c>
       <c r="E108" s="20" t="n">
-        <v>3727</v>
+        <v>3726.889</v>
       </c>
       <c r="F108" s="20" t="n">
         <v>6281.791</v>
@@ -32403,7 +32403,7 @@
         <v/>
       </c>
       <c r="L108" s="20" t="n">
-        <v>1989</v>
+        <v>1989.007</v>
       </c>
       <c r="M108" s="4" t="n">
         <v>3436.727</v>
@@ -32641,7 +32641,7 @@
         </is>
       </c>
       <c r="E111" s="20" t="n">
-        <v>4167</v>
+        <v>4166.885</v>
       </c>
       <c r="F111" s="20" t="n">
         <v>3870.535</v>
@@ -32663,7 +32663,7 @@
         <v/>
       </c>
       <c r="L111" s="4" t="n">
-        <v>2513</v>
+        <v>2513.384</v>
       </c>
       <c r="M111" s="4" t="n">
         <v>2465.249</v>
